--- a/MS_Excel_Practical_Exam_Medium_Level (3).xlsx
+++ b/MS_Excel_Practical_Exam_Medium_Level (3).xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25225"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASDC5\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rohit\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8238AFCA-26D8-4A70-9714-6520038DBD90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65598693-DA08-4220-AA9A-95F1E97D34FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="110">
   <si>
     <t>Total Questions: 30</t>
   </si>
@@ -376,6 +375,24 @@
   </si>
   <si>
     <t xml:space="preserve">Filter </t>
+  </si>
+  <si>
+    <t>4,5,8</t>
+  </si>
+  <si>
+    <t>13,14,20,21</t>
+  </si>
+  <si>
+    <t>12,15,22</t>
+  </si>
+  <si>
+    <t>1,2,3,7,9,11 23,24,27</t>
+  </si>
+  <si>
+    <t>Removed Duplicates</t>
+  </si>
+  <si>
+    <t>29,30</t>
   </si>
 </sst>
 </file>
@@ -414,7 +431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -448,6 +465,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -485,10 +520,10 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="thin">
+      <left style="thin">
         <color indexed="64"/>
-      </right>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -497,31 +532,44 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -534,6 +582,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -941,6 +992,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -948,7 +1000,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1078,7 +1129,7 @@
         <c:idx val="1"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -1134,7 +1185,7 @@
         <c:idx val="2"/>
         <c:spPr>
           <a:solidFill>
-            <a:schemeClr val="accent3"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -1584,6 +1635,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1591,7 +1643,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -3049,6 +3100,79 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF493F6E-C65C-408C-99DF-B1E454D7B453}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Products">
+  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="15">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="3"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of TotalP_Amount" fld="9" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="1">
+    <chartFormat chart="0" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{87F33AAA-7855-4E00-8A72-19FE4AD5DF35}" name="PivotTable3" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1">
   <location ref="A11:D17" firstHeaderRow="0" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="4">
@@ -3149,7 +3273,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A0688657-8DFE-4E82-8766-7CDC040916DE}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="Regions">
   <location ref="D3:E8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="15">
@@ -3210,79 +3334,6 @@
   <dataFields count="1">
     <dataField name="Sum of TotalP_Amount" fld="9" baseField="0" baseItem="0"/>
   </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{AF493F6E-C65C-408C-99DF-B1E454D7B453}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="1" rowHeaderCaption="Products">
-  <location ref="A3:B7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
-  <pivotFields count="15">
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="3"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colItems count="1">
-    <i/>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Sum of TotalP_Amount" fld="9" baseField="0" baseItem="0"/>
-  </dataFields>
-  <chartFormats count="1">
-    <chartFormat chart="0" format="0" series="1">
-      <pivotArea type="data" outline="0" fieldPosition="0">
-        <references count="1">
-          <reference field="4294967294" count="1" selected="0">
-            <x v="0"/>
-          </reference>
-        </references>
-      </pivotArea>
-    </chartFormat>
-  </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
@@ -3581,29 +3632,29 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A5"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -3615,96 +3666,102 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C79F3976-0862-4AE9-A7E9-C45319424D98}">
-  <dimension ref="A3:E17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:P17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>96</v>
       </c>
       <c r="B3" t="s">
         <v>95</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="6" t="s">
         <v>97</v>
       </c>
       <c r="E3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="9" t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4">
         <v>265500</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="10">
+      <c r="E4">
         <v>60480</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5">
         <v>151200</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="10">
+      <c r="E5">
         <v>173400</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="9" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A6" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6">
         <v>60480</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="C6" s="11">
+        <v>16</v>
+      </c>
+      <c r="D6" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6">
         <v>190200</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="9" t="s">
+      <c r="F6" s="11">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A7" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7">
         <v>477180</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7">
         <v>53100</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D8" s="9" t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="D8" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8">
         <v>477180</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>93</v>
       </c>
       <c r="B11" t="s">
@@ -3717,87 +3774,93 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A12" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12">
         <v>65</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12">
         <v>70</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A13" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13">
         <v>92</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13">
         <v>89</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13">
         <v>94</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+      <c r="P13" s="11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A14" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14">
         <v>78</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14">
         <v>82</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14">
         <v>85</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15">
         <v>88</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15">
         <v>91</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15">
         <v>90</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A16" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16">
         <v>55</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16">
         <v>60</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16">
         <v>58</v>
       </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+      <c r="E16" s="11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A17" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17">
         <v>378</v>
       </c>
-      <c r="C17" s="10">
+      <c r="C17">
         <v>392</v>
       </c>
-      <c r="D17" s="10">
+      <c r="D17">
         <v>399</v>
       </c>
     </row>
@@ -3809,41 +3872,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O27"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:R27"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="2" t="s">
         <v>10</v>
       </c>
       <c r="H1" s="2" t="s">
@@ -3858,39 +3921,39 @@
       <c r="K1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="L1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="M1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="N1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="O1" s="2" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>301</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="9">
         <v>2</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="9">
         <v>45000</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="9" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="3">
@@ -3913,39 +3976,39 @@
         <f t="shared" ref="L2:L7" si="3">TEXT(G2,"mmmm")</f>
         <v>January</v>
       </c>
-      <c r="M2" s="5" t="str">
+      <c r="M2" s="3" t="str">
         <f>INDEX(Product_Master!$A$2:$C$4,MATCH(D2,Product_Master!$A$2:$A$4,0),2)</f>
         <v>Electronics</v>
       </c>
-      <c r="N2" t="str">
+      <c r="N2" s="3" t="str">
         <f>LEFT(C2,2)</f>
         <v>Am</v>
       </c>
-      <c r="O2">
+      <c r="O2" s="3">
         <f>ROUND(F2,1)</f>
         <v>45000</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>306</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="9">
         <v>2</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="9">
         <v>45000</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="9" t="s">
         <v>26</v>
       </c>
       <c r="H3" s="3">
@@ -3968,39 +4031,44 @@
         <f t="shared" si="3"/>
         <v>January</v>
       </c>
-      <c r="M3" s="5" t="str">
+      <c r="M3" s="3" t="str">
         <f>INDEX(Product_Master!$A$2:$C$4,MATCH(D3,Product_Master!$A$2:$A$4,0),2)</f>
         <v>Electronics</v>
       </c>
-      <c r="N3" t="str">
+      <c r="N3" s="3" t="str">
         <f t="shared" ref="N3:N7" si="4">LEFT(C3,2)</f>
         <v>Ri</v>
       </c>
-      <c r="O3">
+      <c r="O3" s="3">
         <f t="shared" ref="O3:O7" si="5">ROUND(F3,1)</f>
         <v>45000</v>
       </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="P3" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q3" s="14"/>
+      <c r="R3" s="14"/>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>302</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="9">
         <v>5</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="9">
         <v>15000</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="9" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="3">
@@ -4023,39 +4091,39 @@
         <f t="shared" si="3"/>
         <v>January</v>
       </c>
-      <c r="M4" s="5" t="str">
+      <c r="M4" s="3" t="str">
         <f>INDEX(Product_Master!$A$2:$C$4,MATCH(D4,Product_Master!$A$2:$A$4,0),2)</f>
         <v>Electronics</v>
       </c>
-      <c r="N4" t="str">
+      <c r="N4" s="3" t="str">
         <f t="shared" si="4"/>
         <v>Ri</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="3">
         <f t="shared" si="5"/>
         <v>15000</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>305</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="9">
         <v>4</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="9">
         <v>15000</v>
       </c>
-      <c r="G5" t="s">
+      <c r="G5" s="9" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="3">
@@ -4078,39 +4146,39 @@
         <f t="shared" si="3"/>
         <v>January</v>
       </c>
-      <c r="M5" s="5" t="str">
+      <c r="M5" s="3" t="str">
         <f>INDEX(Product_Master!$A$2:$C$4,MATCH(D5,Product_Master!$A$2:$A$4,0),2)</f>
         <v>Electronics</v>
       </c>
-      <c r="N5" t="str">
+      <c r="N5" s="3" t="str">
         <f t="shared" si="4"/>
         <v>Am</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="3">
         <f t="shared" si="5"/>
         <v>15000</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>303</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="9">
         <v>3</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="9">
         <v>18000</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="9" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="3">
@@ -4133,39 +4201,39 @@
         <f t="shared" si="3"/>
         <v>January</v>
       </c>
-      <c r="M6" s="5" t="str">
+      <c r="M6" s="3" t="str">
         <f>INDEX(Product_Master!$A$2:$C$4,MATCH(D6,Product_Master!$A$2:$A$4,0),2)</f>
         <v>Electronics</v>
       </c>
-      <c r="N6" t="str">
+      <c r="N6" s="3" t="str">
         <f t="shared" si="4"/>
         <v>Ku</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="3">
         <f t="shared" si="5"/>
         <v>18000</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A7" s="9">
         <v>304</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="9">
         <v>1</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="9">
         <v>45000</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="10">
         <v>45669</v>
       </c>
       <c r="H7" s="3">
@@ -4176,7 +4244,7 @@
         <f>VLOOKUP(D7,Product_Master!$A$2:$C$4,3,0)*H7/100</f>
         <v>8100</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="4">
         <f t="shared" si="1"/>
         <v>53100</v>
       </c>
@@ -4188,175 +4256,200 @@
         <f t="shared" si="3"/>
         <v>January</v>
       </c>
-      <c r="M7" s="5" t="str">
+      <c r="M7" s="3" t="str">
         <f>INDEX(Product_Master!$A$2:$C$4,MATCH(D7,Product_Master!$A$2:$A$4,0),2)</f>
         <v>Electronics</v>
       </c>
-      <c r="N7" t="str">
+      <c r="N7" s="3" t="str">
         <f t="shared" si="4"/>
         <v>Ne</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="3">
         <f t="shared" si="5"/>
         <v>45000</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A8" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20">
         <f>SUM(J2:J7)</f>
         <v>477180</v>
       </c>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
-      <c r="K8" s="13"/>
-      <c r="L8" s="13"/>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
+      <c r="I8" s="20"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="20"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="20"/>
+      <c r="N8" s="20"/>
+      <c r="O8" s="20"/>
+      <c r="Q8" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="R8" s="15"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A9" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13">
+      <c r="B9" s="20"/>
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20">
         <f>MAX(J2:J7)</f>
         <v>106200</v>
       </c>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
+      <c r="I9" s="20"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="20"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="20"/>
+      <c r="N9" s="20"/>
+      <c r="O9" s="20"/>
+      <c r="Q9" s="15"/>
+      <c r="R9" s="15"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A10" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="13"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13">
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20">
         <f>MIN(J2:J7)</f>
         <v>53100</v>
       </c>
-      <c r="I10" s="13"/>
-      <c r="J10" s="13"/>
-      <c r="K10" s="13"/>
-      <c r="L10" s="13"/>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="I10" s="20"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="20"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="20"/>
+      <c r="N10" s="20"/>
+      <c r="O10" s="20"/>
+      <c r="Q10" s="15"/>
+      <c r="R10" s="15"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A11" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13">
+      <c r="B11" s="20"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="20"/>
+      <c r="F11" s="20"/>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20">
         <f>COUNTA(A2:A7)</f>
         <v>6</v>
       </c>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="13"/>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="20"/>
+      <c r="N11" s="20"/>
+      <c r="O11" s="20"/>
+      <c r="Q11" s="15"/>
+      <c r="R11" s="15"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A12" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18">
         <f>COUNTIFS(D2:D7,"Laptop",B2:B7,"North")</f>
         <v>1</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="I12" s="18"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+      <c r="N12" s="11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A13" s="22" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="17"/>
-      <c r="J13" s="17"/>
-      <c r="M13" s="16" t="s">
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="M13" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="N13" s="16"/>
-      <c r="O13" s="16"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="str" cm="1">
+      <c r="N13" s="21"/>
+      <c r="O13" s="21"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str" cm="1">
         <f t="array" ref="A14:J20">_xlfn._xlws.SORT(A1:J7,10,-1)</f>
         <v>Order_ID</v>
       </c>
-      <c r="B14" s="7" t="str">
+      <c r="B14" s="5" t="str">
         <v>Region</v>
       </c>
-      <c r="C14" s="7" t="str">
+      <c r="C14" s="5" t="str">
         <v>Salesperson</v>
       </c>
-      <c r="D14" s="7" t="str">
+      <c r="D14" s="5" t="str">
         <v>Product</v>
       </c>
-      <c r="E14" s="7" t="str">
+      <c r="E14" s="5" t="str">
         <v>Quantity</v>
       </c>
-      <c r="F14" s="7" t="str">
+      <c r="F14" s="5" t="str">
         <v>Unit_Price</v>
       </c>
-      <c r="G14" s="7" t="str">
+      <c r="G14" s="5" t="str">
         <v>Sales_Date</v>
       </c>
-      <c r="H14" s="7" t="str">
+      <c r="H14" s="5" t="str">
         <v>Sales_Amount</v>
       </c>
-      <c r="I14" s="7" t="str">
+      <c r="I14" s="5" t="str">
         <v>GST_Amount</v>
       </c>
-      <c r="J14" s="7" t="str">
+      <c r="J14" s="5" t="str">
         <v>TotalP_Amount</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="N14" s="15">
+      <c r="N14" s="19">
         <f ca="1">SUMIF(B2:B7,M14,J2:J6)</f>
         <v>173400</v>
       </c>
-      <c r="O14" s="15"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O14" s="19"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>301</v>
       </c>
@@ -4390,13 +4483,16 @@
       <c r="M15" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="15">
+      <c r="N15" s="19">
         <f ca="1">SUMIF(B3:B8,M15,J3:J7)</f>
         <v>190200</v>
       </c>
-      <c r="O15" s="15"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O15" s="19"/>
+      <c r="P15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>306</v>
       </c>
@@ -4427,16 +4523,19 @@
       <c r="J16">
         <v>106200</v>
       </c>
+      <c r="K16" s="11">
+        <v>10</v>
+      </c>
       <c r="M16" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N16" s="15">
+      <c r="N16" s="19">
         <f ca="1">SUMIF(B4:B11,M16,J4:J8)</f>
         <v>60480</v>
       </c>
-      <c r="O16" s="15"/>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O16" s="19"/>
+    </row>
+    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>302</v>
       </c>
@@ -4470,13 +4569,13 @@
       <c r="M17" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="N17" s="15">
+      <c r="N17" s="19">
         <f ca="1">SUMIF(B5:B12,M17,J5:J11)</f>
         <v>53100</v>
       </c>
-      <c r="O17" s="15"/>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="O17" s="19"/>
+    </row>
+    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>305</v>
       </c>
@@ -4508,7 +4607,7 @@
         <v>67200</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>303</v>
       </c>
@@ -4540,7 +4639,7 @@
         <v>60480</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>304</v>
       </c>
@@ -4572,18 +4671,100 @@
         <v>53100</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A25" s="12" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="J22" s="16" t="s">
+        <v>108</v>
+      </c>
+      <c r="K22" s="16"/>
+      <c r="L22" s="16"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16"/>
+      <c r="P22" s="16"/>
+    </row>
+    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="J23" cm="1">
+        <f t="array" ref="J23:P26">INDEX(A2:G7,MATCH(_xlfn.UNIQUE(C2:C7),C2:C7,0),{1,2,3,4,5,6,7})</f>
+        <v>301</v>
+      </c>
+      <c r="K23" t="str">
+        <v>North</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Amit</v>
+      </c>
+      <c r="M23" t="str">
+        <v>Laptop</v>
+      </c>
+      <c r="N23">
+        <v>2</v>
+      </c>
+      <c r="O23">
+        <v>45000</v>
+      </c>
+      <c r="P23" t="str">
+        <v>05-01-2025</v>
+      </c>
+    </row>
+    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="J24">
+        <v>306</v>
+      </c>
+      <c r="K24" t="str">
+        <v>South</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Riya</v>
+      </c>
+      <c r="M24" t="str">
+        <v>Laptop</v>
+      </c>
+      <c r="N24">
+        <v>2</v>
+      </c>
+      <c r="O24">
+        <v>45000</v>
+      </c>
+      <c r="P24" t="str">
+        <v>18-01-2025</v>
+      </c>
+      <c r="R24" s="11">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A25" s="17" t="s">
         <v>103</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="B25" s="17"/>
+      <c r="C25" s="17"/>
+      <c r="D25" s="17"/>
+      <c r="E25" s="17"/>
+      <c r="F25" s="17"/>
+      <c r="G25" s="17"/>
+      <c r="J25">
+        <v>303</v>
+      </c>
+      <c r="K25" t="str">
+        <v>East</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Kunal</v>
+      </c>
+      <c r="M25" t="str">
+        <v>Tablet</v>
+      </c>
+      <c r="N25">
+        <v>3</v>
+      </c>
+      <c r="O25">
+        <v>18000</v>
+      </c>
+      <c r="P25" t="str">
+        <v>10-01-2025</v>
+      </c>
+    </row>
+    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A26" cm="1">
         <f t="array" ref="A26:G27">_xlfn._xlws.FILTER(A2:G7,(E2:E7&gt;1)*(D2:D7="Laptop"),"")</f>
         <v>301</v>
@@ -4606,8 +4787,32 @@
       <c r="G26" t="str">
         <v>05-01-2025</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H26" s="11">
+        <v>25</v>
+      </c>
+      <c r="J26">
+        <v>304</v>
+      </c>
+      <c r="K26" t="str">
+        <v>West</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Neha</v>
+      </c>
+      <c r="M26" t="str">
+        <v>Laptop</v>
+      </c>
+      <c r="N26">
+        <v>1</v>
+      </c>
+      <c r="O26">
+        <v>45000</v>
+      </c>
+      <c r="P26">
+        <v>45669</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>306</v>
       </c>
@@ -4634,24 +4839,27 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L7">
     <sortCondition descending="1" ref="J2:J7"/>
   </sortState>
-  <mergeCells count="17">
-    <mergeCell ref="H8:L8"/>
-    <mergeCell ref="A8:G8"/>
+  <mergeCells count="20">
     <mergeCell ref="A11:G11"/>
     <mergeCell ref="M13:O13"/>
     <mergeCell ref="N14:O14"/>
     <mergeCell ref="A13:J13"/>
+    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="Q8:R11"/>
+    <mergeCell ref="J22:P22"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A12:G12"/>
+    <mergeCell ref="H12:L12"/>
     <mergeCell ref="N15:O15"/>
     <mergeCell ref="N16:O16"/>
     <mergeCell ref="N17:O17"/>
     <mergeCell ref="A9:G9"/>
     <mergeCell ref="A10:G10"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="H9:L9"/>
-    <mergeCell ref="H11:L11"/>
-    <mergeCell ref="H10:L10"/>
-    <mergeCell ref="A12:G12"/>
-    <mergeCell ref="H12:L12"/>
+    <mergeCell ref="H8:O8"/>
+    <mergeCell ref="H9:O9"/>
+    <mergeCell ref="H10:O10"/>
+    <mergeCell ref="H11:O11"/>
+    <mergeCell ref="A8:G8"/>
   </mergeCells>
   <conditionalFormatting sqref="J2:J7">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
@@ -4666,9 +4874,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
@@ -4679,7 +4887,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -4690,7 +4898,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -4701,7 +4909,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -4719,253 +4927,280 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:N12"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="12" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="9">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="9">
         <v>78</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="9">
         <v>82</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="9">
         <v>85</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="9">
         <v>92</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="9">
         <f>AVERAGE(C2:F2)</f>
         <v>84.25</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" s="9" t="str">
         <f>IF(F2&gt;=85,"Eligible","Not Eligible")</f>
         <v>Eligible</v>
       </c>
-      <c r="I2" t="str">
+      <c r="I2" s="9" t="str">
         <f>_xlfn.CONCAT(A2,"_",B2)</f>
         <v>1_Rahul</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A3" s="9">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="9">
         <v>88</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="9">
         <v>91</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="9">
         <v>90</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="9">
         <v>96</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="9">
         <f t="shared" ref="G3:G6" si="0">AVERAGE(C3:F3)</f>
         <v>91.25</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H3" s="9" t="str">
         <f t="shared" ref="H3:H6" si="1">IF(F3&gt;=85,"Eligible","Not Eligible")</f>
         <v>Eligible</v>
       </c>
-      <c r="I3" t="str">
+      <c r="I3" s="9" t="str">
         <f t="shared" ref="I3:I6" si="2">_xlfn.CONCAT(A3,"_",B3)</f>
         <v>2_Sneha</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+      <c r="K3" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="L3" s="14"/>
+      <c r="M3" s="14"/>
+      <c r="N3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A4" s="9">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="9">
         <v>65</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="9">
         <v>70</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="9">
         <v>72</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="9">
         <v>85</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="9">
         <f t="shared" si="0"/>
         <v>73</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H4" s="9" t="str">
         <f t="shared" si="1"/>
         <v>Eligible</v>
       </c>
-      <c r="I4" t="str">
+      <c r="I4" s="9" t="str">
         <f t="shared" si="2"/>
         <v>3_Arjun</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5" s="9">
         <v>4</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="9">
         <v>92</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="9">
         <v>89</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="9">
         <v>94</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="9">
         <v>98</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="9">
         <f t="shared" si="0"/>
         <v>93.25</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H5" s="9" t="str">
         <f t="shared" si="1"/>
         <v>Eligible</v>
       </c>
-      <c r="I5" t="str">
+      <c r="I5" s="9" t="str">
         <f t="shared" si="2"/>
         <v>4_Pooja</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6" s="9">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="9">
         <v>55</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="9">
         <v>60</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="9">
         <v>58</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="9">
         <v>80</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="9">
         <f t="shared" si="0"/>
         <v>63.25</v>
       </c>
-      <c r="H6" t="str">
+      <c r="H6" s="9" t="str">
         <f t="shared" si="1"/>
         <v>Not Eligible</v>
       </c>
-      <c r="I6" t="str">
+      <c r="I6" s="9" t="str">
         <f t="shared" si="2"/>
         <v>5_Vikas</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="19"/>
-      <c r="C9" s="19"/>
-      <c r="D9" s="19"/>
-      <c r="E9" s="19" t="str">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24" t="str">
         <f>INDEX(B2:G6,MATCH(MAX(G2:G6),G2:G6,0),1)</f>
         <v>Pooja</v>
       </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="19"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-      <c r="D10" s="14"/>
-      <c r="E10" s="14">
+      <c r="B10" s="25"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25">
         <f>COUNTIF(F2:F6,"&gt;90")</f>
         <v>3</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="I10" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A11" s="23" t="s">
         <v>86</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18">
+      <c r="B11" s="23"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+      <c r="E11" s="23">
         <f>MEDIAN(D2:D6)</f>
         <v>82</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F11" s="23"/>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>87</v>
       </c>
-      <c r="E12" s="18">
+      <c r="E12" s="23">
         <f>_xlfn.STDEV.S(E2:E6)</f>
         <v>14.737706741552426</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <sheetProtection algorithmName="SHA-512" hashValue="U+2D/fcbv+HXbY3SC+zXn4L5X+7+2DziSpvZCnRGqDY6AZf3baKDqL0dk0A2xy2rAIHNKnC0BchkSgMn+sn9mg==" saltValue="Bxs+xc/hmXJ9dembwA/0/w==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <mergeCells count="9">
+    <mergeCell ref="K3:M3"/>
+    <mergeCell ref="I10:K10"/>
     <mergeCell ref="E12:G12"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="E9:G9"/>
@@ -4981,9 +5216,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>41</v>
       </c>
@@ -4991,7 +5226,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>42</v>
       </c>
@@ -4999,7 +5234,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>43</v>
       </c>
@@ -5007,7 +5242,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -5015,7 +5250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>45</v>
       </c>
@@ -5023,7 +5258,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>46</v>
       </c>
@@ -5031,7 +5266,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>47</v>
       </c>
@@ -5039,7 +5274,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>48</v>
       </c>
@@ -5047,7 +5282,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -5055,7 +5290,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>50</v>
       </c>
@@ -5063,7 +5298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>51</v>
       </c>
@@ -5071,7 +5306,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>52</v>
       </c>
@@ -5079,7 +5314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>53</v>
       </c>
@@ -5087,7 +5322,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>54</v>
       </c>
@@ -5095,7 +5330,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -5103,7 +5338,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -5111,7 +5346,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>57</v>
       </c>
@@ -5119,7 +5354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>58</v>
       </c>
@@ -5127,7 +5362,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>59</v>
       </c>
@@ -5135,7 +5370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>60</v>
       </c>
@@ -5143,7 +5378,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>61</v>
       </c>
@@ -5151,7 +5386,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>62</v>
       </c>
@@ -5159,7 +5394,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>63</v>
       </c>
@@ -5167,7 +5402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>64</v>
       </c>
@@ -5175,7 +5410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>65</v>
       </c>
@@ -5183,7 +5418,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>66</v>
       </c>
@@ -5191,7 +5426,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>67</v>
       </c>
@@ -5199,7 +5434,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>68</v>
       </c>
@@ -5207,7 +5442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>69</v>
       </c>
@@ -5215,7 +5450,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>70</v>
       </c>
@@ -5223,7 +5458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="J32">
         <f>SUM(J1:J30)</f>
         <v>60</v>
@@ -5237,23 +5472,23 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CE160309-1180-4376-BF95-D41FB1F93250}">
   <dimension ref="A1:M6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
@@ -5292,7 +5527,7 @@
         <v>Sales_Date</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>301</v>
       </c>
@@ -5330,7 +5565,7 @@
         <v>05-01-2025</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>306</v>
       </c>
@@ -5368,7 +5603,7 @@
         <v>18-01-2025</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>303</v>
       </c>
@@ -5409,7 +5644,7 @@
         <v>10-01-2025</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>304</v>
       </c>
@@ -5428,7 +5663,7 @@
       <c r="F6">
         <v>45000</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="8">
         <v>45669</v>
       </c>
       <c r="I6" t="str">
